--- a/data/trans_camb/P43E-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P43E-Habitat-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-3,37</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,37</t>
+          <t>-3,54</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -0,29</t>
+          <t>-9,96; 0,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 1,7</t>
+          <t>-8,4; 1,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -0,29</t>
+          <t>-9,96; 0,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 1,7</t>
+          <t>-8,4; 1,3</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-20,17%</t>
+          <t>-21,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-20,17%</t>
+          <t>-21,18%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,18; -1,13</t>
+          <t>-52,53; 0,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 11,89</t>
+          <t>-43,2; 9,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,18; -1,13</t>
+          <t>-52,53; 0,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 11,89</t>
+          <t>-43,2; 9,12</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-4,02</t>
+          <t>-3,62</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,02</t>
+          <t>-3,62</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -5,21</t>
+          <t>-14,02; -5,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 1,02</t>
+          <t>-8,98; 0,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -5,21</t>
+          <t>-14,02; -5,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 1,02</t>
+          <t>-8,98; 0,64</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-16,21%</t>
+          <t>-14,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-16,21%</t>
+          <t>-14,59%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,17; -23,02</t>
+          <t>-51,55; -23,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 5,35</t>
+          <t>-32,69; 2,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,17; -23,02</t>
+          <t>-51,55; -23,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 5,35</t>
+          <t>-32,69; 2,57</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>6,1</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -1,76</t>
+          <t>-12,85; -2,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 10,92</t>
+          <t>-0,24; 11,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -1,76</t>
+          <t>-12,85; -2,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 10,92</t>
+          <t>-0,24; 11,85</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,23; -8,67</t>
+          <t>-46,12; -9,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 48,6</t>
+          <t>-0,73; 54,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,23; -8,67</t>
+          <t>-46,12; -9,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 48,6</t>
+          <t>-0,73; 54,04</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>5,06</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 0,29</t>
+          <t>-9,5; -0,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 6,8</t>
+          <t>0,57; 9,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 0,29</t>
+          <t>-9,5; -0,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 6,8</t>
+          <t>0,57; 9,84</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 1,68</t>
+          <t>-36,04; 0,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 30,58</t>
+          <t>2,15; 46,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 1,68</t>
+          <t>-36,04; 0,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 30,58</t>
+          <t>2,15; 46,17</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>1,55</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -4,22</t>
+          <t>-9,14; -4,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,86</t>
+          <t>-1,2; 4,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -4,22</t>
+          <t>-9,14; -4,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,86</t>
+          <t>-1,2; 4,16</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-0,38%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0,38%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-37,29; -19,49</t>
+          <t>-37,77; -18,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 12,94</t>
+          <t>-4,99; 19,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,29; -19,49</t>
+          <t>-37,77; -18,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 12,94</t>
+          <t>-4,99; 19,32</t>
         </is>
       </c>
     </row>
